--- a/resources/templates/standard/K1200-03.xlsx
+++ b/resources/templates/standard/K1200-03.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="14">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">결
 재</t>
@@ -614,7 +617,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -628,18 +633,18 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P1" s="3"/>
       <c r="Q1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R1" s="3"/>
       <c r="S1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
@@ -716,23 +721,23 @@
     </row>
     <row r="4" ht="21.95" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
@@ -746,7 +751,7 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" s="5"/>
       <c r="U4" s="11"/>
@@ -834,7 +839,7 @@
       <c r="D6" s="16"/>
       <c r="E6" s="14"/>
       <c r="F6" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
@@ -867,7 +872,7 @@
       <c r="D7" s="16"/>
       <c r="E7" s="14"/>
       <c r="F7" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" s="21"/>
       <c r="H7" s="21"/>
@@ -903,7 +908,7 @@
       <c r="D8" s="16"/>
       <c r="E8" s="14"/>
       <c r="F8" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="18"/>
       <c r="H8" s="18"/>
@@ -936,7 +941,7 @@
       <c r="D9" s="16"/>
       <c r="E9" s="14"/>
       <c r="F9" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
@@ -972,7 +977,7 @@
       <c r="D10" s="16"/>
       <c r="E10" s="14"/>
       <c r="F10" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
@@ -1005,7 +1010,7 @@
       <c r="D11" s="16"/>
       <c r="E11" s="14"/>
       <c r="F11" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
@@ -1041,7 +1046,7 @@
       <c r="D12" s="16"/>
       <c r="E12" s="14"/>
       <c r="F12" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
@@ -1074,7 +1079,7 @@
       <c r="D13" s="16"/>
       <c r="E13" s="14"/>
       <c r="F13" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
@@ -1110,7 +1115,7 @@
       <c r="D14" s="16"/>
       <c r="E14" s="14"/>
       <c r="F14" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
@@ -1143,7 +1148,7 @@
       <c r="D15" s="16"/>
       <c r="E15" s="14"/>
       <c r="F15" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="21"/>
@@ -1179,7 +1184,7 @@
       <c r="D16" s="16"/>
       <c r="E16" s="14"/>
       <c r="F16" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
@@ -1212,7 +1217,7 @@
       <c r="D17" s="16"/>
       <c r="E17" s="14"/>
       <c r="F17" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
@@ -1248,7 +1253,7 @@
       <c r="D18" s="16"/>
       <c r="E18" s="14"/>
       <c r="F18" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="18"/>
@@ -1281,7 +1286,7 @@
       <c r="D19" s="16"/>
       <c r="E19" s="14"/>
       <c r="F19" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
@@ -1317,7 +1322,7 @@
       <c r="D20" s="16"/>
       <c r="E20" s="14"/>
       <c r="F20" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="18"/>
       <c r="H20" s="18"/>
@@ -1350,7 +1355,7 @@
       <c r="D21" s="16"/>
       <c r="E21" s="14"/>
       <c r="F21" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
@@ -1385,7 +1390,7 @@
       <c r="D22" s="16"/>
       <c r="E22" s="14"/>
       <c r="F22" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
@@ -1418,7 +1423,7 @@
       <c r="D23" s="16"/>
       <c r="E23" s="14"/>
       <c r="F23" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="21"/>
@@ -1453,7 +1458,7 @@
       <c r="D24" s="22"/>
       <c r="E24" s="14"/>
       <c r="F24" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
@@ -1486,7 +1491,7 @@
       <c r="D25" s="22"/>
       <c r="E25" s="14"/>
       <c r="F25" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="21"/>
@@ -1521,7 +1526,7 @@
       <c r="D26" s="22"/>
       <c r="E26" s="14"/>
       <c r="F26" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
@@ -1554,7 +1559,7 @@
       <c r="D27" s="22"/>
       <c r="E27" s="14"/>
       <c r="F27" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="21"/>
@@ -1589,7 +1594,7 @@
       <c r="D28" s="22"/>
       <c r="E28" s="14"/>
       <c r="F28" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" s="18"/>
       <c r="H28" s="18"/>
@@ -1622,7 +1627,7 @@
       <c r="D29" s="22"/>
       <c r="E29" s="14"/>
       <c r="F29" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="21"/>
@@ -1657,7 +1662,7 @@
       <c r="D30" s="22"/>
       <c r="E30" s="14"/>
       <c r="F30" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" s="18"/>
       <c r="H30" s="18"/>
@@ -1690,7 +1695,7 @@
       <c r="D31" s="22"/>
       <c r="E31" s="14"/>
       <c r="F31" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="21"/>
